--- a/_posts/2023-02-26-delinquancefivefactormodel/delinq.xlsx
+++ b/_posts/2023-02-26-delinquancefivefactormodel/delinq.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25831"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ouriagan\Documents\blog\_posts\2023-02-26-delinquancefivefactormodel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BB7EE82-1E53-4B77-ABAA-8094E1185912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9706C51-0851-4333-A423-CB5FCE83857E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="1095" windowWidth="12975" windowHeight="12735" xr2:uid="{511E6DC4-25CB-4046-B852-A3F54DA287BE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{511E6DC4-25CB-4046-B852-A3F54DA287BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -44,12 +44,6 @@
     <t>fait de délinquance</t>
   </si>
   <si>
-    <t>Bagarre individuel</t>
-  </si>
-  <si>
-    <t>Blessure en groupe</t>
-  </si>
-  <si>
     <t>Pris quelque chose dans une boutique sans le payer</t>
   </si>
   <si>
@@ -93,6 +87,12 @@
   </si>
   <si>
     <t>Utilisé une arme de quelque sorte pour obtenir quelque chose de quelqu’un</t>
+  </si>
+  <si>
+    <t>Fait partie d’un groupe blessant physiquement un individu</t>
+  </si>
+  <si>
+    <t>Fait partie d’un groupe commençant une bagarre avec un autre groupe</t>
   </si>
 </sst>
 </file>
@@ -477,138 +477,138 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B2">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B3">
-        <v>34</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B4">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
         <v>9</v>
-      </c>
-      <c r="B7">
-        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B8">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B9">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B10">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B11">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B13">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B14">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B15">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B16">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B17">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
